--- a/input/validation/15-5/instance-16.xlsx
+++ b/input/validation/15-5/instance-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -517,19 +517,19 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="L2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -559,19 +559,19 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -587,7 +587,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -601,19 +601,19 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -643,58 +643,58 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J-0</t>
+          <t>J-1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>O-04</t>
+          <t>O-10</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -713,33 +713,33 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>O-10</t>
+          <t>O-11</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -755,33 +755,33 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>O-11</t>
+          <t>O-12</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -797,33 +797,33 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>O-12</t>
+          <t>O-13</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -839,33 +839,33 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>O-13</t>
+          <t>O-14</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
         <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -881,72 +881,72 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O-14</t>
+          <t>O-15</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J-1</t>
+          <t>J-2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>O-15</t>
+          <t>O-20</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L12" t="n">
         <v>16</v>
@@ -965,33 +965,33 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>O-20</t>
+          <t>O-21</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1007,30 +1007,30 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>O-21</t>
+          <t>O-22</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1049,33 +1049,33 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>O-22</t>
+          <t>O-23</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -1091,33 +1091,33 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>O-23</t>
+          <t>O-24</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -1133,33 +1133,33 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>O-24</t>
+          <t>O-25</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L17" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1189,19 +1189,19 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -1217,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1231,19 +1231,19 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1315,19 +1315,19 @@
         <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -1343,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1357,16 +1357,16 @@
         <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1375,43 +1375,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J-4</t>
+          <t>J-3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>O-40</t>
+          <t>O-35</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I23" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K23" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L23" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -1427,33 +1427,33 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>O-41</t>
+          <t>O-40</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -1469,24 +1469,24 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>O-42</t>
+          <t>O-41</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1511,24 +1511,24 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>O-43</t>
+          <t>O-42</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1537,46 +1537,46 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-4</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>O-50</t>
+          <t>O-43</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I27" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1592,33 +1592,33 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D28" t="n">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>O-51</t>
+          <t>O-50</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1634,36 +1634,36 @@
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D29" t="n">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>O-52</t>
+          <t>O-51</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
+        <v>12</v>
+      </c>
+      <c r="K29" t="n">
         <v>10</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
@@ -1676,162 +1676,162 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D30" t="n">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>O-53</t>
+          <t>O-52</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>22</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>O-60</t>
+          <t>O-53</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
+        <v>14</v>
+      </c>
+      <c r="J31" t="n">
         <v>12</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
       <c r="K31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>O-61</t>
+          <t>O-54</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>30</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J32" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>O-62</t>
+          <t>O-55</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>31</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L33" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1844,24 +1844,24 @@
         <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D34" t="n">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>O-63</t>
+          <t>O-60</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -1879,40 +1879,40 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D35" t="n">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>O-70</t>
+          <t>O-61</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -1921,121 +1921,121 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D36" t="n">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>O-71</t>
+          <t>O-62</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>34</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D37" t="n">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>O-72</t>
+          <t>O-63</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D38" t="n">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>O-73</t>
+          <t>O-64</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>36</v>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2047,21 +2047,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D39" t="n">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>O-80</t>
+          <t>O-70</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2071,39 +2071,39 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I39" t="n">
+        <v>14</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>15</v>
-      </c>
-      <c r="J39" t="n">
-        <v>15</v>
-      </c>
-      <c r="K39" t="n">
-        <v>17</v>
-      </c>
-      <c r="L39" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>O-81</t>
+          <t>O-71</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2113,39 +2113,39 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I40" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L40" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D41" t="n">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>O-82</t>
+          <t>O-72</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -2155,39 +2155,39 @@
         <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K41" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D42" t="n">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>O-83</t>
+          <t>O-73</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2203,33 +2203,33 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K42" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>J-9</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C43" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D43" t="n">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>O-90</t>
+          <t>O-80</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2248,30 +2248,30 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="L43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>J-9</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D44" t="n">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>O-91</t>
+          <t>O-81</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2281,39 +2281,39 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L44" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>J-9</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D45" t="n">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>O-92</t>
+          <t>O-82</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2323,13 +2323,13 @@
         <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2341,21 +2341,21 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>J-9</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C46" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D46" t="n">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>O-93</t>
+          <t>O-83</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2365,19 +2365,19 @@
         <v>3</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
@@ -2390,33 +2390,33 @@
         <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D47" t="n">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>O-94</t>
+          <t>O-90</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>45</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>16</v>
@@ -2425,76 +2425,76 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>J-10</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C48" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D48" t="n">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>O-100</t>
+          <t>O-91</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L48" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>J-10</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D49" t="n">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>O-101</t>
+          <t>O-92</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>47</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2509,40 +2509,40 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>J-10</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D50" t="n">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>O-102</t>
+          <t>O-93</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>48</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J50" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K50" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2551,85 +2551,85 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>J-10</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C51" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D51" t="n">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>O-103</t>
+          <t>O-94</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>49</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
+        <v>8</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
         <v>12</v>
-      </c>
-      <c r="J51" t="n">
-        <v>14</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>J-10</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D52" t="n">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>O-104</t>
+          <t>O-95</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>50</v>
       </c>
       <c r="G52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H52" t="n">
+        <v>10</v>
+      </c>
+      <c r="I52" t="n">
+        <v>10</v>
+      </c>
+      <c r="J52" t="n">
+        <v>14</v>
+      </c>
+      <c r="K52" t="n">
         <v>13</v>
       </c>
-      <c r="I52" t="n">
+      <c r="L52" t="n">
         <v>11</v>
-      </c>
-      <c r="J52" t="n">
-        <v>10</v>
-      </c>
-      <c r="K52" t="n">
-        <v>10</v>
-      </c>
-      <c r="L52" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="53">
@@ -2642,321 +2642,321 @@
         <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="D53" t="n">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>O-105</t>
+          <t>O-100</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>51</v>
       </c>
       <c r="G53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>J-11</t>
+          <t>J-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C54" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D54" t="n">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>O-110</t>
+          <t>O-101</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>52</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>J-11</t>
+          <t>J-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D55" t="n">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>O-111</t>
+          <t>O-102</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>53</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>J-11</t>
+          <t>J-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D56" t="n">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>O-112</t>
+          <t>O-103</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>54</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="K56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>J-11</t>
+          <t>J-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C57" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D57" t="n">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>O-113</t>
+          <t>O-104</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>55</v>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J57" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>J-12</t>
+          <t>J-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C58" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D58" t="n">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>O-120</t>
+          <t>O-105</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>56</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J58" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>J-12</t>
+          <t>J-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C59" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="D59" t="n">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>O-121</t>
+          <t>O-110</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>57</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>J-12</t>
+          <t>J-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C60" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="D60" t="n">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>O-122</t>
+          <t>O-111</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>58</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2965,172 +2965,172 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>J-12</t>
+          <t>J-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C61" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="D61" t="n">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>O-123</t>
+          <t>O-112</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>59</v>
       </c>
       <c r="G61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>J-12</t>
+          <t>J-11</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C62" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="D62" t="n">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>O-124</t>
+          <t>O-113</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>60</v>
       </c>
       <c r="G62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H62" t="n">
+        <v>19</v>
+      </c>
+      <c r="I62" t="n">
+        <v>17</v>
+      </c>
+      <c r="J62" t="n">
+        <v>14</v>
+      </c>
+      <c r="K62" t="n">
         <v>16</v>
       </c>
-      <c r="I62" t="n">
-        <v>16</v>
-      </c>
-      <c r="J62" t="n">
-        <v>15</v>
-      </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
         <v>18</v>
-      </c>
-      <c r="L62" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>J-13</t>
+          <t>J-11</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C63" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D63" t="n">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>O-130</t>
+          <t>O-114</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>61</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L63" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>J-13</t>
+          <t>J-11</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C64" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D64" t="n">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>O-131</t>
+          <t>O-115</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>62</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H64" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J64" t="n">
         <v>14</v>
       </c>
       <c r="K64" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L64" t="n">
         <v>13</v>
@@ -3139,40 +3139,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>J-13</t>
+          <t>J-12</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D65" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>O-132</t>
+          <t>O-120</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>63</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K65" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3181,70 +3181,70 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>J-13</t>
+          <t>J-12</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C66" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D66" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>O-133</t>
+          <t>O-121</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>64</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J66" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K66" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L66" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>J-13</t>
+          <t>J-12</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C67" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D67" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>O-134</t>
+          <t>O-122</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>65</v>
       </c>
       <c r="G67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3253,10 +3253,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K67" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3265,79 +3265,79 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>J-13</t>
+          <t>J-12</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C68" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D68" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>O-135</t>
+          <t>O-123</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>66</v>
       </c>
       <c r="G68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
+        <v>10</v>
+      </c>
+      <c r="L68" t="n">
         <v>9</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>J-14</t>
+          <t>J-12</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C69" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D69" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>O-140</t>
+          <t>O-124</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>67</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J69" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3349,82 +3349,82 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>J-14</t>
+          <t>J-13</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C70" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D70" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>O-141</t>
+          <t>O-130</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>68</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>J-14</t>
+          <t>J-13</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C71" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D71" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>O-142</t>
+          <t>O-131</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>69</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>15</v>
+      </c>
+      <c r="J71" t="n">
+        <v>15</v>
+      </c>
+      <c r="K71" t="n">
         <v>13</v>
-      </c>
-      <c r="I71" t="n">
-        <v>14</v>
-      </c>
-      <c r="J71" t="n">
-        <v>14</v>
-      </c>
-      <c r="K71" t="n">
-        <v>18</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3433,85 +3433,337 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>J-14</t>
+          <t>J-13</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C72" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D72" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>O-143</t>
+          <t>O-132</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>70</v>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K72" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>J-14</t>
+          <t>J-13</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C73" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D73" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>O-144</t>
+          <t>O-133</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>71</v>
       </c>
       <c r="G73" t="n">
+        <v>3</v>
+      </c>
+      <c r="H73" t="n">
+        <v>19</v>
+      </c>
+      <c r="I73" t="n">
+        <v>14</v>
+      </c>
+      <c r="J73" t="n">
+        <v>13</v>
+      </c>
+      <c r="K73" t="n">
+        <v>16</v>
+      </c>
+      <c r="L73" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>J-14</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>14</v>
+      </c>
+      <c r="C74" t="n">
+        <v>148</v>
+      </c>
+      <c r="D74" t="n">
+        <v>160</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>O-140</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>72</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>16</v>
+      </c>
+      <c r="L74" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>J-14</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>14</v>
+      </c>
+      <c r="C75" t="n">
+        <v>148</v>
+      </c>
+      <c r="D75" t="n">
+        <v>160</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>O-141</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>73</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>14</v>
+      </c>
+      <c r="J75" t="n">
+        <v>18</v>
+      </c>
+      <c r="K75" t="n">
+        <v>18</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>J-14</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>14</v>
+      </c>
+      <c r="C76" t="n">
+        <v>148</v>
+      </c>
+      <c r="D76" t="n">
+        <v>160</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>O-142</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>74</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>10</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>13</v>
+      </c>
+      <c r="K76" t="n">
+        <v>14</v>
+      </c>
+      <c r="L76" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>J-14</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>14</v>
+      </c>
+      <c r="C77" t="n">
+        <v>148</v>
+      </c>
+      <c r="D77" t="n">
+        <v>160</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>O-143</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>75</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>16</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>J-14</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>14</v>
+      </c>
+      <c r="C78" t="n">
+        <v>148</v>
+      </c>
+      <c r="D78" t="n">
+        <v>160</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>O-144</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>76</v>
+      </c>
+      <c r="G78" t="n">
         <v>4</v>
       </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>15</v>
+      </c>
+      <c r="K78" t="n">
+        <v>18</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>J-14</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>14</v>
+      </c>
+      <c r="C79" t="n">
+        <v>148</v>
+      </c>
+      <c r="D79" t="n">
+        <v>160</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>O-145</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>77</v>
+      </c>
+      <c r="G79" t="n">
+        <v>5</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>24</v>
+      </c>
+      <c r="J79" t="n">
         <v>22</v>
       </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
+      <c r="K79" t="n">
+        <v>23</v>
+      </c>
+      <c r="L79" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/input/validation/15-5/instance-16.xlsx
+++ b/input/validation/15-5/instance-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -517,19 +517,19 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -562,16 +562,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -587,7 +587,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -643,16 +643,16 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>13</v>
+      </c>
+      <c r="J5" t="n">
         <v>12</v>
       </c>
-      <c r="I5" t="n">
-        <v>11</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>11</v>
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -685,19 +685,19 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -755,7 +755,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -769,19 +769,19 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
         <v>3</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>19</v>
-      </c>
-      <c r="I9" t="n">
-        <v>20</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -829,37 +829,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J-1</t>
+          <t>J-2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>O-14</t>
+          <t>O-20</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -871,40 +871,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J-1</t>
+          <t>J-2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O-15</t>
+          <t>O-21</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L11" t="n">
         <v>16</v>
@@ -923,18 +923,18 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>O-20</t>
+          <t>O-22</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -943,13 +943,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -965,18 +965,18 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>O-21</t>
+          <t>O-23</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -985,13 +985,13 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -1007,108 +1007,108 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>O-22</t>
+          <t>O-24</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
+        <v>18</v>
+      </c>
+      <c r="I14" t="n">
         <v>17</v>
       </c>
-      <c r="I14" t="n">
-        <v>21</v>
-      </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K14" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J-2</t>
+          <t>J-3</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>139</v>
+        <v>46</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>O-23</t>
+          <t>O-30</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>10</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J-2</t>
+          <t>J-3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>139</v>
+        <v>46</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>O-24</t>
+          <t>O-31</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1117,49 +1117,49 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J-2</t>
+          <t>J-3</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>139</v>
+        <v>46</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>O-25</t>
+          <t>O-32</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1175,114 +1175,114 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>139</v>
+        <v>46</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>O-30</t>
+          <t>O-33</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J-3</t>
+          <t>J-4</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>O-31</t>
+          <t>O-40</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J-3</t>
+          <t>J-4</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>O-32</t>
+          <t>O-41</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1291,82 +1291,82 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J-3</t>
+          <t>J-4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>O-33</t>
+          <t>O-42</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>19</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" t="n">
         <v>10</v>
-      </c>
-      <c r="J21" t="n">
-        <v>11</v>
       </c>
       <c r="K21" t="n">
         <v>9</v>
       </c>
       <c r="L21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J-3</t>
+          <t>J-4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>O-34</t>
+          <t>O-43</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1375,43 +1375,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J-3</t>
+          <t>J-4</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>O-35</t>
+          <t>O-44</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>13</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
       <c r="J23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1427,66 +1427,66 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>O-40</t>
+          <t>O-45</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J-4</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>O-41</t>
+          <t>O-50</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1501,85 +1501,85 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J-4</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>O-42</t>
+          <t>O-51</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J-4</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>O-43</t>
+          <t>O-52</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -1592,33 +1592,33 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>O-50</t>
+          <t>O-53</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1634,36 +1634,36 @@
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>O-51</t>
+          <t>O-54</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1676,162 +1676,162 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>O-52</t>
+          <t>O-55</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D31" t="n">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>O-53</t>
+          <t>O-60</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D32" t="n">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>O-54</t>
+          <t>O-61</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>30</v>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D33" t="n">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>O-55</t>
+          <t>O-62</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>31</v>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K33" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
@@ -1844,36 +1844,36 @@
         <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D34" t="n">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>O-60</t>
+          <t>O-63</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
@@ -1886,36 +1886,36 @@
         <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D35" t="n">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>O-61</t>
+          <t>O-64</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -1928,21 +1928,21 @@
         <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D36" t="n">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>O-62</t>
+          <t>O-65</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>34</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1954,94 +1954,94 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L36" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D37" t="n">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>O-63</t>
+          <t>O-70</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D38" t="n">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>O-64</t>
+          <t>O-71</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>36</v>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
+        <v>12</v>
+      </c>
+      <c r="I38" t="n">
         <v>14</v>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
       <c r="J38" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
@@ -2054,33 +2054,33 @@
         <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D39" t="n">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>O-70</t>
+          <t>O-72</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>37</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I39" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L39" t="n">
         <v>15</v>
@@ -2096,120 +2096,120 @@
         <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D40" t="n">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>O-71</t>
+          <t>O-73</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>38</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K40" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C41" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D41" t="n">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>O-72</t>
+          <t>O-80</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>39</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C42" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D42" t="n">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>O-73</t>
+          <t>O-81</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>40</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J42" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L42" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
@@ -2222,36 +2222,36 @@
         <v>8</v>
       </c>
       <c r="C43" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="D43" t="n">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>O-80</t>
+          <t>O-82</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>41</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K43" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
@@ -2264,36 +2264,36 @@
         <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="D44" t="n">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>O-81</t>
+          <t>O-83</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L44" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2306,33 +2306,33 @@
         <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="D45" t="n">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>O-82</t>
+          <t>O-84</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>43</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J45" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2341,43 +2341,43 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D46" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>O-83</t>
+          <t>O-90</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2390,36 +2390,36 @@
         <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="D47" t="n">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>O-90</t>
+          <t>O-91</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>45</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L47" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2432,21 +2432,21 @@
         <v>9</v>
       </c>
       <c r="C48" t="n">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="D48" t="n">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>O-91</t>
+          <t>O-92</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2455,10 +2455,10 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2474,75 +2474,75 @@
         <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="D49" t="n">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>O-92</t>
+          <t>O-93</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>47</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>J-9</t>
+          <t>J-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C50" t="n">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="D50" t="n">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>O-93</t>
+          <t>O-100</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>48</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I50" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>11</v>
-      </c>
-      <c r="K50" t="n">
-        <v>13</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2551,85 +2551,85 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>J-9</t>
+          <t>J-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C51" t="n">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="D51" t="n">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>O-94</t>
+          <t>O-101</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>49</v>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L51" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>J-9</t>
+          <t>J-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="D52" t="n">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>O-95</t>
+          <t>O-102</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>50</v>
       </c>
       <c r="G52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>9</v>
+      </c>
+      <c r="J52" t="n">
+        <v>13</v>
+      </c>
+      <c r="K52" t="n">
+        <v>9</v>
+      </c>
+      <c r="L52" t="n">
         <v>10</v>
-      </c>
-      <c r="I52" t="n">
-        <v>10</v>
-      </c>
-      <c r="J52" t="n">
-        <v>14</v>
-      </c>
-      <c r="K52" t="n">
-        <v>13</v>
-      </c>
-      <c r="L52" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="53">
@@ -2642,237 +2642,237 @@
         <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="D53" t="n">
-        <v>151</v>
+        <v>68</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>O-100</t>
+          <t>O-103</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>51</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J53" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L53" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>J-10</t>
+          <t>J-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C54" t="n">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="D54" t="n">
-        <v>151</v>
+        <v>62</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>O-101</t>
+          <t>O-110</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>52</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L54" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>J-10</t>
+          <t>J-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C55" t="n">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="D55" t="n">
-        <v>151</v>
+        <v>62</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>O-102</t>
+          <t>O-111</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>53</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I55" t="n">
+        <v>13</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
         <v>16</v>
       </c>
-      <c r="J55" t="n">
-        <v>16</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>J-10</t>
+          <t>J-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" t="n">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="D56" t="n">
-        <v>151</v>
+        <v>62</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>O-103</t>
+          <t>O-112</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>54</v>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>J-10</t>
+          <t>J-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C57" t="n">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="D57" t="n">
-        <v>151</v>
+        <v>62</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>O-104</t>
+          <t>O-113</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>55</v>
       </c>
       <c r="G57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H57" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I57" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>J-10</t>
+          <t>J-12</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C58" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D58" t="n">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>O-105</t>
+          <t>O-120</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>56</v>
       </c>
       <c r="G58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I58" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2887,118 +2887,118 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>J-11</t>
+          <t>J-12</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C59" t="n">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="D59" t="n">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>O-110</t>
+          <t>O-121</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>57</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J59" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="L59" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>J-11</t>
+          <t>J-12</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C60" t="n">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="D60" t="n">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>O-111</t>
+          <t>O-122</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>58</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L60" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>J-11</t>
+          <t>J-12</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C61" t="n">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="D61" t="n">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>O-112</t>
+          <t>O-123</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>59</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3007,762 +3007,384 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>J-11</t>
+          <t>J-13</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C62" t="n">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="D62" t="n">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>O-113</t>
+          <t>O-130</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>60</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I62" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>J-11</t>
+          <t>J-13</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C63" t="n">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="D63" t="n">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>O-114</t>
+          <t>O-131</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>61</v>
       </c>
       <c r="G63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K63" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L63" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>J-11</t>
+          <t>J-13</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C64" t="n">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="D64" t="n">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>O-115</t>
+          <t>O-132</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>62</v>
       </c>
       <c r="G64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H64" t="n">
         <v>12</v>
       </c>
       <c r="I64" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K64" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>J-12</t>
+          <t>J-13</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C65" t="n">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="D65" t="n">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>O-120</t>
+          <t>O-133</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>63</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>J-12</t>
+          <t>J-14</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C66" t="n">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="D66" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>O-121</t>
+          <t>O-140</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>64</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I66" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K66" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>J-12</t>
+          <t>J-14</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C67" t="n">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="D67" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>O-122</t>
+          <t>O-141</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>65</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>J-12</t>
+          <t>J-14</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C68" t="n">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="D68" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>O-123</t>
+          <t>O-142</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>66</v>
       </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I68" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L68" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>J-12</t>
+          <t>J-14</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C69" t="n">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="D69" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>O-124</t>
+          <t>O-143</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>67</v>
       </c>
       <c r="G69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I69" t="n">
+        <v>11</v>
+      </c>
+      <c r="J69" t="n">
+        <v>9</v>
+      </c>
+      <c r="K69" t="n">
+        <v>11</v>
+      </c>
+      <c r="L69" t="n">
         <v>12</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>J-13</t>
+          <t>J-14</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C70" t="n">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="D70" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>O-130</t>
+          <t>O-144</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>68</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H70" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>J-13</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>13</v>
-      </c>
-      <c r="C71" t="n">
-        <v>135</v>
-      </c>
-      <c r="D71" t="n">
-        <v>93</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>O-131</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>69</v>
-      </c>
-      <c r="G71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>15</v>
-      </c>
-      <c r="J71" t="n">
-        <v>15</v>
-      </c>
-      <c r="K71" t="n">
-        <v>13</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>J-13</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>13</v>
-      </c>
-      <c r="C72" t="n">
-        <v>135</v>
-      </c>
-      <c r="D72" t="n">
-        <v>93</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>O-132</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>70</v>
-      </c>
-      <c r="G72" t="n">
-        <v>2</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>18</v>
-      </c>
-      <c r="J72" t="n">
-        <v>14</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>J-13</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>13</v>
-      </c>
-      <c r="C73" t="n">
-        <v>135</v>
-      </c>
-      <c r="D73" t="n">
-        <v>93</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>O-133</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>71</v>
-      </c>
-      <c r="G73" t="n">
-        <v>3</v>
-      </c>
-      <c r="H73" t="n">
-        <v>19</v>
-      </c>
-      <c r="I73" t="n">
-        <v>14</v>
-      </c>
-      <c r="J73" t="n">
-        <v>13</v>
-      </c>
-      <c r="K73" t="n">
-        <v>16</v>
-      </c>
-      <c r="L73" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>J-14</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>14</v>
-      </c>
-      <c r="C74" t="n">
-        <v>148</v>
-      </c>
-      <c r="D74" t="n">
-        <v>160</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>O-140</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>72</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="n">
-        <v>16</v>
-      </c>
-      <c r="L74" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>J-14</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>14</v>
-      </c>
-      <c r="C75" t="n">
-        <v>148</v>
-      </c>
-      <c r="D75" t="n">
-        <v>160</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>O-141</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>73</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="n">
-        <v>14</v>
-      </c>
-      <c r="J75" t="n">
-        <v>18</v>
-      </c>
-      <c r="K75" t="n">
-        <v>18</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>J-14</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>14</v>
-      </c>
-      <c r="C76" t="n">
-        <v>148</v>
-      </c>
-      <c r="D76" t="n">
-        <v>160</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>O-142</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>74</v>
-      </c>
-      <c r="G76" t="n">
-        <v>2</v>
-      </c>
-      <c r="H76" t="n">
-        <v>10</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="n">
-        <v>13</v>
-      </c>
-      <c r="K76" t="n">
-        <v>14</v>
-      </c>
-      <c r="L76" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>J-14</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>14</v>
-      </c>
-      <c r="C77" t="n">
-        <v>148</v>
-      </c>
-      <c r="D77" t="n">
-        <v>160</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>O-143</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>75</v>
-      </c>
-      <c r="G77" t="n">
-        <v>3</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
-        <v>16</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>J-14</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>14</v>
-      </c>
-      <c r="C78" t="n">
-        <v>148</v>
-      </c>
-      <c r="D78" t="n">
-        <v>160</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>O-144</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>76</v>
-      </c>
-      <c r="G78" t="n">
-        <v>4</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="n">
-        <v>15</v>
-      </c>
-      <c r="K78" t="n">
-        <v>18</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>J-14</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>14</v>
-      </c>
-      <c r="C79" t="n">
-        <v>148</v>
-      </c>
-      <c r="D79" t="n">
-        <v>160</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>O-145</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>77</v>
-      </c>
-      <c r="G79" t="n">
-        <v>5</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="n">
-        <v>24</v>
-      </c>
-      <c r="J79" t="n">
-        <v>22</v>
-      </c>
-      <c r="K79" t="n">
-        <v>23</v>
-      </c>
-      <c r="L79" t="n">
         <v>17</v>
       </c>
     </row>
